--- a/docs/data/history.xlsx
+++ b/docs/data/history.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J113"/>
+  <dimension ref="A1:J114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4298,6 +4298,40 @@
         <v>3.64</v>
       </c>
     </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B114" t="n">
+        <v>3</v>
+      </c>
+      <c r="C114" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="D114" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="E114" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="F114" t="n">
+        <v>4.13</v>
+      </c>
+      <c r="G114" t="n">
+        <v>4.547</v>
+      </c>
+      <c r="H114" t="n">
+        <v>4.685</v>
+      </c>
+      <c r="I114" t="n">
+        <v>4.02</v>
+      </c>
+      <c r="J114" t="n">
+        <v>3.62</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
